--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FB9F31-4A96-4785-BF17-3BED1A4CA091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD8BED3-39DD-41B3-8843-C5C49A57C621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9915" yWindow="0" windowWidth="19320" windowHeight="23205" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
+    <workbookView xWindow="45" yWindow="-14340" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,42 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -110,42 +145,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF002060"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1305,6 +1305,9 @@
       <c r="A29">
         <v>1</v>
       </c>
+      <c r="L29">
+        <v>5</v>
+      </c>
       <c r="S29">
         <v>1</v>
       </c>
@@ -4869,28 +4872,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="2">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="3">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="3">
       <formula>NOT(ISERROR(SEARCH("3",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="4">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="4">
       <formula>NOT(ISERROR(SEARCH("4",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="5">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="5">
       <formula>NOT(ISERROR(SEARCH("5",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="9">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="9">
       <formula>NOT(ISERROR(SEARCH("9",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="6">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="6">
       <formula>NOT(ISERROR(SEARCH("6",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="7">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="7">
       <formula>NOT(ISERROR(SEARCH("7",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD8BED3-39DD-41B3-8843-C5C49A57C621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E01DDC2-C489-4A0F-8256-92666FB067CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="45" yWindow="-14340" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>

--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E01DDC2-C489-4A0F-8256-92666FB067CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E1271B-82C5-491A-87BC-97460ECD27B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="-14340" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
+    <workbookView xWindow="1950" yWindow="1545" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4407,6 +4407,15 @@
       <c r="A131">
         <v>1</v>
       </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
       <c r="M131">
         <v>1</v>
       </c>
@@ -4497,6 +4506,15 @@
     </row>
     <row r="132" spans="1:80" x14ac:dyDescent="0.4">
       <c r="A132">
+        <v>1</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132">
         <v>1</v>
       </c>
       <c r="M132">

--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E1271B-82C5-491A-87BC-97460ECD27B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBA1535-0CB6-429B-9662-10E6FC987E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1545" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
+    <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -699,6 +699,9 @@
       <c r="A11">
         <v>1</v>
       </c>
+      <c r="AP11">
+        <v>3</v>
+      </c>
       <c r="BA11">
         <v>4</v>
       </c>
@@ -1029,9 +1032,15 @@
       <c r="AR20">
         <v>1</v>
       </c>
+      <c r="BE20">
+        <v>3</v>
+      </c>
       <c r="BJ20">
         <v>4</v>
       </c>
+      <c r="BM20">
+        <v>3</v>
+      </c>
       <c r="CB20">
         <v>1</v>
       </c>
@@ -1229,6 +1238,9 @@
       <c r="BE27">
         <v>1</v>
       </c>
+      <c r="BT27">
+        <v>3</v>
+      </c>
       <c r="BZ27">
         <v>4</v>
       </c>
@@ -1240,8 +1252,11 @@
       <c r="A28">
         <v>1</v>
       </c>
-      <c r="X28">
-        <v>4</v>
+      <c r="R28">
+        <v>3</v>
+      </c>
+      <c r="AA28">
+        <v>3</v>
       </c>
       <c r="AR28">
         <v>1</v>
@@ -1305,8 +1320,11 @@
       <c r="A29">
         <v>1</v>
       </c>
-      <c r="L29">
-        <v>5</v>
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="O29">
+        <v>3</v>
       </c>
       <c r="S29">
         <v>1</v>
@@ -1370,7 +1388,10 @@
       <c r="BE30">
         <v>1</v>
       </c>
-      <c r="BQ30">
+      <c r="BM30">
+        <v>3</v>
+      </c>
+      <c r="BT30">
         <v>3</v>
       </c>
       <c r="CB30">
@@ -1454,7 +1475,7 @@
       <c r="A33">
         <v>1</v>
       </c>
-      <c r="B33">
+      <c r="I33">
         <v>3</v>
       </c>
       <c r="AR33">
@@ -1579,9 +1600,15 @@
       <c r="A37">
         <v>1</v>
       </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
       <c r="M37">
         <v>4</v>
       </c>
+      <c r="Q37">
+        <v>3</v>
+      </c>
       <c r="BE37">
         <v>1</v>
       </c>
@@ -1628,10 +1655,19 @@
       <c r="A39">
         <v>1</v>
       </c>
+      <c r="S39">
+        <v>3</v>
+      </c>
       <c r="W39">
         <v>5</v>
       </c>
-      <c r="AH39">
+      <c r="AA39">
+        <v>3</v>
+      </c>
+      <c r="AD39">
+        <v>3</v>
+      </c>
+      <c r="AL39">
         <v>3</v>
       </c>
       <c r="BE39">
@@ -1768,6 +1804,9 @@
       <c r="A43">
         <v>1</v>
       </c>
+      <c r="BU43">
+        <v>3</v>
+      </c>
       <c r="BZ43">
         <v>5</v>
       </c>
@@ -1951,10 +1990,19 @@
       <c r="A55">
         <v>1</v>
       </c>
+      <c r="AX55">
+        <v>3</v>
+      </c>
       <c r="BB55">
         <v>4</v>
       </c>
-      <c r="BM55">
+      <c r="BD55">
+        <v>3</v>
+      </c>
+      <c r="BJ55">
+        <v>3</v>
+      </c>
+      <c r="BO55">
         <v>3</v>
       </c>
       <c r="CB55">
@@ -2052,6 +2100,9 @@
       <c r="A59">
         <v>1</v>
       </c>
+      <c r="N59">
+        <v>3</v>
+      </c>
       <c r="R59">
         <v>4</v>
       </c>
@@ -2061,6 +2112,9 @@
       <c r="W59">
         <v>1</v>
       </c>
+      <c r="AC59">
+        <v>3</v>
+      </c>
       <c r="AF59">
         <v>4</v>
       </c>
@@ -2076,9 +2130,6 @@
       <c r="AS59">
         <v>1</v>
       </c>
-      <c r="BD59">
-        <v>3</v>
-      </c>
       <c r="BK59">
         <v>1</v>
       </c>
@@ -2724,7 +2775,10 @@
       <c r="A80">
         <v>1</v>
       </c>
-      <c r="W80">
+      <c r="S80">
+        <v>3</v>
+      </c>
+      <c r="Y80">
         <v>3</v>
       </c>
       <c r="AY80">
@@ -2902,6 +2956,9 @@
       <c r="A85">
         <v>1</v>
       </c>
+      <c r="AI85">
+        <v>3</v>
+      </c>
       <c r="AP85">
         <v>5</v>
       </c>
@@ -3166,9 +3223,15 @@
       <c r="A91">
         <v>1</v>
       </c>
+      <c r="L91">
+        <v>3</v>
+      </c>
       <c r="Q91">
         <v>4</v>
       </c>
+      <c r="R91">
+        <v>3</v>
+      </c>
       <c r="AJ91">
         <v>1</v>
       </c>
@@ -3243,8 +3306,11 @@
       <c r="AJ95">
         <v>1</v>
       </c>
-      <c r="AQ95">
-        <v>4</v>
+      <c r="AM95">
+        <v>3</v>
+      </c>
+      <c r="AX95">
+        <v>3</v>
       </c>
       <c r="CB95">
         <v>1</v>
@@ -3486,8 +3552,11 @@
       <c r="AS104">
         <v>1</v>
       </c>
-      <c r="BH104">
-        <v>5</v>
+      <c r="BE104">
+        <v>3</v>
+      </c>
+      <c r="BK104">
+        <v>3</v>
       </c>
       <c r="CB104">
         <v>1</v>
@@ -3766,9 +3835,6 @@
       <c r="BN115">
         <v>1</v>
       </c>
-      <c r="BS115">
-        <v>4</v>
-      </c>
       <c r="BT115">
         <v>1</v>
       </c>
@@ -3786,9 +3852,6 @@
       <c r="T116">
         <v>1</v>
       </c>
-      <c r="V116">
-        <v>4</v>
-      </c>
       <c r="Z116">
         <v>1</v>
       </c>
@@ -3810,8 +3873,11 @@
       <c r="AS116">
         <v>1</v>
       </c>
-      <c r="BH116">
-        <v>5</v>
+      <c r="BD116">
+        <v>3</v>
+      </c>
+      <c r="BJ116">
+        <v>3</v>
       </c>
       <c r="BN116">
         <v>1</v>
@@ -4026,8 +4092,11 @@
       <c r="A122">
         <v>1</v>
       </c>
-      <c r="AR122">
-        <v>4</v>
+      <c r="AN122">
+        <v>3</v>
+      </c>
+      <c r="AT122">
+        <v>3</v>
       </c>
       <c r="CB122">
         <v>1</v>
@@ -4106,10 +4175,7 @@
       <c r="A126">
         <v>1</v>
       </c>
-      <c r="AI126">
-        <v>3</v>
-      </c>
-      <c r="AL126">
+      <c r="AE126">
         <v>3</v>
       </c>
       <c r="AO126">
@@ -4541,9 +4607,6 @@
       <c r="W132">
         <v>1</v>
       </c>
-      <c r="AA132">
-        <v>4</v>
-      </c>
       <c r="AD132">
         <v>1</v>
       </c>
@@ -4609,15 +4672,6 @@
       </c>
       <c r="AY132">
         <v>1</v>
-      </c>
-      <c r="BE132">
-        <v>3</v>
-      </c>
-      <c r="BO132">
-        <v>3</v>
-      </c>
-      <c r="BX132">
-        <v>3</v>
       </c>
       <c r="CB132">
         <v>1</v>

--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBA1535-0CB6-429B-9662-10E6FC987E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D1538B-0849-472F-86A6-4F63FAFE24EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>
@@ -699,6 +699,42 @@
       <c r="A11">
         <v>1</v>
       </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="X11">
+        <v>3</v>
+      </c>
+      <c r="AA11">
+        <v>3</v>
+      </c>
+      <c r="AD11">
+        <v>3</v>
+      </c>
+      <c r="AG11">
+        <v>3</v>
+      </c>
+      <c r="AJ11">
+        <v>3</v>
+      </c>
+      <c r="AM11">
+        <v>3</v>
+      </c>
       <c r="AP11">
         <v>3</v>
       </c>
@@ -902,6 +938,9 @@
       <c r="A15">
         <v>1</v>
       </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
       <c r="AR15">
         <v>1</v>
       </c>
@@ -961,6 +1000,42 @@
       <c r="A19">
         <v>1</v>
       </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>3</v>
+      </c>
+      <c r="T19">
+        <v>3</v>
+      </c>
+      <c r="X19">
+        <v>3</v>
+      </c>
+      <c r="Z19">
+        <v>3</v>
+      </c>
+      <c r="AE19">
+        <v>3</v>
+      </c>
+      <c r="AG19">
+        <v>3</v>
+      </c>
+      <c r="AK19">
+        <v>3</v>
+      </c>
+      <c r="AL19">
+        <v>3</v>
+      </c>
+      <c r="AP19">
+        <v>3</v>
+      </c>
       <c r="AR19">
         <v>1</v>
       </c>
@@ -1092,8 +1167,14 @@
       <c r="A23">
         <v>1</v>
       </c>
+      <c r="AL23">
+        <v>3</v>
+      </c>
       <c r="AR23">
         <v>1</v>
+      </c>
+      <c r="AU23">
+        <v>3</v>
       </c>
       <c r="AY23">
         <v>6</v>
@@ -1194,6 +1275,12 @@
       <c r="A26">
         <v>1</v>
       </c>
+      <c r="AC26">
+        <v>3</v>
+      </c>
+      <c r="AL26">
+        <v>3</v>
+      </c>
       <c r="AR26">
         <v>1</v>
       </c>
@@ -1235,6 +1322,9 @@
       <c r="AR27">
         <v>1</v>
       </c>
+      <c r="BB27">
+        <v>3</v>
+      </c>
       <c r="BE27">
         <v>1</v>
       </c>
@@ -1405,6 +1495,9 @@
       <c r="AR31">
         <v>1</v>
       </c>
+      <c r="AU31">
+        <v>3</v>
+      </c>
       <c r="BE31">
         <v>1</v>
       </c>
@@ -1539,6 +1632,9 @@
       <c r="AR35">
         <v>1</v>
       </c>
+      <c r="BB35">
+        <v>3</v>
+      </c>
       <c r="BE35">
         <v>1</v>
       </c>
@@ -1670,6 +1766,9 @@
       <c r="AL39">
         <v>3</v>
       </c>
+      <c r="AO39">
+        <v>3</v>
+      </c>
       <c r="BE39">
         <v>1</v>
       </c>
@@ -1818,6 +1917,9 @@
       <c r="A44">
         <v>1</v>
       </c>
+      <c r="J44">
+        <v>3</v>
+      </c>
       <c r="Y44">
         <v>2</v>
       </c>
@@ -1865,6 +1967,30 @@
       <c r="A45">
         <v>1</v>
       </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
       <c r="AK45">
         <v>2</v>
       </c>
@@ -1930,6 +2056,12 @@
       <c r="A49">
         <v>1</v>
       </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="Q49">
+        <v>1</v>
+      </c>
       <c r="CB49">
         <v>1</v>
       </c>
@@ -1974,6 +2106,9 @@
       <c r="A53">
         <v>1</v>
       </c>
+      <c r="U53">
+        <v>1</v>
+      </c>
       <c r="CB53">
         <v>1</v>
       </c>
@@ -2348,6 +2483,9 @@
       <c r="A63">
         <v>1</v>
       </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
       <c r="CB63">
         <v>1</v>
       </c>
@@ -2371,6 +2509,12 @@
       <c r="F64">
         <v>1</v>
       </c>
+      <c r="N64">
+        <v>3</v>
+      </c>
+      <c r="T64">
+        <v>3</v>
+      </c>
       <c r="CB64">
         <v>1</v>
       </c>
@@ -2394,6 +2538,30 @@
       <c r="S65">
         <v>1</v>
       </c>
+      <c r="AF65">
+        <v>3</v>
+      </c>
+      <c r="AN65">
+        <v>3</v>
+      </c>
+      <c r="AZ65">
+        <v>3</v>
+      </c>
+      <c r="BF65">
+        <v>3</v>
+      </c>
+      <c r="BI65">
+        <v>3</v>
+      </c>
+      <c r="BP65">
+        <v>3</v>
+      </c>
+      <c r="BS65">
+        <v>3</v>
+      </c>
+      <c r="BX65">
+        <v>3</v>
+      </c>
       <c r="CB65">
         <v>1</v>
       </c>
@@ -2402,6 +2570,18 @@
       <c r="A66">
         <v>1</v>
       </c>
+      <c r="G66">
+        <v>3</v>
+      </c>
+      <c r="L66">
+        <v>3</v>
+      </c>
+      <c r="U66">
+        <v>3</v>
+      </c>
+      <c r="AC66">
+        <v>3</v>
+      </c>
       <c r="AG66">
         <v>1</v>
       </c>
@@ -2509,6 +2689,12 @@
       <c r="AB67">
         <v>1</v>
       </c>
+      <c r="AP67">
+        <v>3</v>
+      </c>
+      <c r="AX67">
+        <v>3</v>
+      </c>
       <c r="CB67">
         <v>1</v>
       </c>
@@ -2554,6 +2740,9 @@
       <c r="A70">
         <v>1</v>
       </c>
+      <c r="BY70">
+        <v>3</v>
+      </c>
       <c r="CB70">
         <v>1</v>
       </c>
@@ -2693,6 +2882,12 @@
       <c r="A75">
         <v>1</v>
       </c>
+      <c r="BP75">
+        <v>3</v>
+      </c>
+      <c r="BX75">
+        <v>3</v>
+      </c>
       <c r="CB75">
         <v>1</v>
       </c>
@@ -2729,6 +2924,12 @@
     <row r="77" spans="1:80" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>1</v>
+      </c>
+      <c r="BD77">
+        <v>3</v>
+      </c>
+      <c r="BL77">
+        <v>3</v>
       </c>
       <c r="CB77">
         <v>1</v>

--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D1538B-0849-472F-86A6-4F63FAFE24EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E6F5D8-32D2-4876-8D84-DA1D83E3BDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
+    <workbookView xWindow="75" yWindow="-14820" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -655,6 +655,66 @@
       <c r="A7">
         <v>1</v>
       </c>
+      <c r="AQ7">
+        <v>2</v>
+      </c>
+      <c r="AR7">
+        <v>2</v>
+      </c>
+      <c r="AS7">
+        <v>2</v>
+      </c>
+      <c r="AT7">
+        <v>2</v>
+      </c>
+      <c r="AU7">
+        <v>2</v>
+      </c>
+      <c r="AV7">
+        <v>2</v>
+      </c>
+      <c r="BB7">
+        <v>2</v>
+      </c>
+      <c r="BC7">
+        <v>2</v>
+      </c>
+      <c r="BD7">
+        <v>2</v>
+      </c>
+      <c r="BE7">
+        <v>2</v>
+      </c>
+      <c r="BF7">
+        <v>2</v>
+      </c>
+      <c r="BG7">
+        <v>2</v>
+      </c>
+      <c r="BH7">
+        <v>2</v>
+      </c>
+      <c r="BN7">
+        <v>2</v>
+      </c>
+      <c r="BO7">
+        <v>2</v>
+      </c>
+      <c r="BP7">
+        <v>2</v>
+      </c>
+      <c r="BQ7">
+        <v>2</v>
+      </c>
+      <c r="BR7">
+        <v>2</v>
+      </c>
+      <c r="BS7">
+        <v>2</v>
+      </c>
+      <c r="BT7">
+        <v>2</v>
+      </c>
       <c r="CB7">
         <v>1</v>
       </c>
@@ -663,6 +723,9 @@
       <c r="A8">
         <v>1</v>
       </c>
+      <c r="BY8">
+        <v>9</v>
+      </c>
       <c r="CB8">
         <v>1</v>
       </c>
@@ -671,8 +734,20 @@
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="BQ9">
-        <v>9</v>
+      <c r="BW9">
+        <v>1</v>
+      </c>
+      <c r="BX9">
+        <v>1</v>
+      </c>
+      <c r="BY9">
+        <v>1</v>
+      </c>
+      <c r="BZ9">
+        <v>1</v>
+      </c>
+      <c r="CA9">
+        <v>1</v>
       </c>
       <c r="CB9">
         <v>1</v>
@@ -682,13 +757,19 @@
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="BP10">
-        <v>1</v>
-      </c>
-      <c r="BQ10">
-        <v>1</v>
-      </c>
-      <c r="BR10">
+      <c r="BW10">
+        <v>1</v>
+      </c>
+      <c r="BX10">
+        <v>1</v>
+      </c>
+      <c r="BY10">
+        <v>1</v>
+      </c>
+      <c r="BZ10">
+        <v>1</v>
+      </c>
+      <c r="CA10">
         <v>1</v>
       </c>
       <c r="CB10">
@@ -744,13 +825,19 @@
       <c r="BJ11">
         <v>5</v>
       </c>
-      <c r="BP11">
-        <v>1</v>
-      </c>
-      <c r="BQ11">
-        <v>1</v>
-      </c>
-      <c r="BR11">
+      <c r="BW11">
+        <v>1</v>
+      </c>
+      <c r="BX11">
+        <v>1</v>
+      </c>
+      <c r="BY11">
+        <v>1</v>
+      </c>
+      <c r="BZ11">
+        <v>1</v>
+      </c>
+      <c r="CA11">
         <v>1</v>
       </c>
       <c r="CB11">
@@ -1107,7 +1194,7 @@
       <c r="AR20">
         <v>1</v>
       </c>
-      <c r="BE20">
+      <c r="BG20">
         <v>3</v>
       </c>
       <c r="BJ20">
@@ -1127,12 +1214,6 @@
       <c r="AR21">
         <v>1</v>
       </c>
-      <c r="BF21">
-        <v>1</v>
-      </c>
-      <c r="BG21">
-        <v>1</v>
-      </c>
       <c r="BH21">
         <v>1</v>
       </c>
@@ -1179,8 +1260,8 @@
       <c r="AY23">
         <v>6</v>
       </c>
-      <c r="BE23">
-        <v>1</v>
+      <c r="BF23">
+        <v>3</v>
       </c>
       <c r="CB23">
         <v>1</v>

--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E6F5D8-32D2-4876-8D84-DA1D83E3BDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF7B5AC-933B-4FB0-AA08-1721E96EE42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="75" yWindow="-14820" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>
@@ -1319,6 +1319,12 @@
       <c r="BE24">
         <v>1</v>
       </c>
+      <c r="BM24">
+        <v>3</v>
+      </c>
+      <c r="BS24">
+        <v>3</v>
+      </c>
       <c r="CB24">
         <v>1</v>
       </c>
@@ -1658,6 +1664,12 @@
       <c r="BE33">
         <v>1</v>
       </c>
+      <c r="BH33">
+        <v>3</v>
+      </c>
+      <c r="BL33">
+        <v>3</v>
+      </c>
       <c r="CB33">
         <v>1</v>
       </c>
@@ -1719,6 +1731,12 @@
       <c r="BE35">
         <v>1</v>
       </c>
+      <c r="BN35">
+        <v>3</v>
+      </c>
+      <c r="BR35">
+        <v>3</v>
+      </c>
       <c r="CB35">
         <v>1</v>
       </c>
@@ -1853,6 +1871,12 @@
       <c r="BE39">
         <v>1</v>
       </c>
+      <c r="BR39">
+        <v>3</v>
+      </c>
+      <c r="BV39">
+        <v>3</v>
+      </c>
       <c r="CB39">
         <v>1</v>
       </c>
@@ -2106,6 +2130,12 @@
       <c r="A47">
         <v>1</v>
       </c>
+      <c r="BO47">
+        <v>3</v>
+      </c>
+      <c r="BU47">
+        <v>3</v>
+      </c>
       <c r="CB47">
         <v>1</v>
       </c>
@@ -2159,6 +2189,12 @@
       <c r="A51">
         <v>1</v>
       </c>
+      <c r="BU51">
+        <v>3</v>
+      </c>
+      <c r="BZ51">
+        <v>3</v>
+      </c>
       <c r="CB51">
         <v>1</v>
       </c>
@@ -2316,6 +2352,12 @@
       <c r="A59">
         <v>1</v>
       </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="K59">
+        <v>3</v>
+      </c>
       <c r="N59">
         <v>3</v>
       </c>
@@ -3049,6 +3091,12 @@
       <c r="A79">
         <v>1</v>
       </c>
+      <c r="AX79">
+        <v>3</v>
+      </c>
+      <c r="BA79">
+        <v>3</v>
+      </c>
       <c r="CB79">
         <v>1</v>
       </c>
@@ -3057,10 +3105,22 @@
       <c r="A80">
         <v>1</v>
       </c>
+      <c r="I80">
+        <v>3</v>
+      </c>
+      <c r="O80">
+        <v>3</v>
+      </c>
       <c r="S80">
         <v>3</v>
       </c>
       <c r="Y80">
+        <v>3</v>
+      </c>
+      <c r="AC80">
+        <v>3</v>
+      </c>
+      <c r="AI80">
         <v>3</v>
       </c>
       <c r="AY80">
@@ -3122,11 +3182,17 @@
       <c r="AH81">
         <v>1</v>
       </c>
+      <c r="AV81">
+        <v>3</v>
+      </c>
       <c r="AY81">
         <v>1</v>
       </c>
       <c r="AZ81">
         <v>1</v>
+      </c>
+      <c r="BC81">
+        <v>3</v>
       </c>
       <c r="CB81">
         <v>1</v>
@@ -3162,6 +3228,12 @@
       <c r="A83">
         <v>1</v>
       </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="AT83">
+        <v>3</v>
+      </c>
       <c r="AW83">
         <v>1</v>
       </c>
@@ -3179,6 +3251,9 @@
       </c>
       <c r="BB83">
         <v>1</v>
+      </c>
+      <c r="BE83">
+        <v>3</v>
       </c>
       <c r="CB83">
         <v>1</v>
@@ -3274,6 +3349,9 @@
       <c r="BD85">
         <v>1</v>
       </c>
+      <c r="BK85">
+        <v>3</v>
+      </c>
       <c r="CB85">
         <v>1</v>
       </c>
@@ -3371,6 +3449,12 @@
       <c r="A87">
         <v>1</v>
       </c>
+      <c r="F87">
+        <v>3</v>
+      </c>
+      <c r="K87">
+        <v>3</v>
+      </c>
       <c r="AJ87">
         <v>1</v>
       </c>
@@ -3514,6 +3598,12 @@
       <c r="R91">
         <v>3</v>
       </c>
+      <c r="V91">
+        <v>3</v>
+      </c>
+      <c r="AA91">
+        <v>3</v>
+      </c>
       <c r="AJ91">
         <v>1</v>
       </c>
@@ -3585,6 +3675,12 @@
       <c r="A95">
         <v>1</v>
       </c>
+      <c r="AB95">
+        <v>3</v>
+      </c>
+      <c r="AF95">
+        <v>3</v>
+      </c>
       <c r="AJ95">
         <v>1</v>
       </c>
@@ -3652,6 +3748,12 @@
       <c r="A97">
         <v>1</v>
       </c>
+      <c r="R97">
+        <v>3</v>
+      </c>
+      <c r="V97">
+        <v>3</v>
+      </c>
       <c r="AJ97">
         <v>1</v>
       </c>
@@ -3675,6 +3777,9 @@
       <c r="U98">
         <v>1</v>
       </c>
+      <c r="AG98">
+        <v>3</v>
+      </c>
       <c r="AJ98">
         <v>1</v>
       </c>
@@ -3701,6 +3806,12 @@
       <c r="AS99">
         <v>1</v>
       </c>
+      <c r="AY99">
+        <v>3</v>
+      </c>
+      <c r="BE99">
+        <v>3</v>
+      </c>
       <c r="CB99">
         <v>1</v>
       </c>
@@ -3709,6 +3820,12 @@
       <c r="A100">
         <v>1</v>
       </c>
+      <c r="M100">
+        <v>3</v>
+      </c>
+      <c r="Q100">
+        <v>3</v>
+      </c>
       <c r="AJ100">
         <v>1</v>
       </c>
@@ -3747,8 +3864,23 @@
       <c r="P101">
         <v>1</v>
       </c>
+      <c r="W101">
+        <v>3</v>
+      </c>
+      <c r="Z101">
+        <v>3</v>
+      </c>
+      <c r="AC101">
+        <v>3</v>
+      </c>
+      <c r="AF101">
+        <v>3</v>
+      </c>
       <c r="AJ101">
         <v>1</v>
+      </c>
+      <c r="AQ101">
+        <v>3</v>
       </c>
       <c r="AS101">
         <v>1</v>
@@ -3805,6 +3937,12 @@
       <c r="A103">
         <v>1</v>
       </c>
+      <c r="G103">
+        <v>3</v>
+      </c>
+      <c r="K103">
+        <v>3</v>
+      </c>
       <c r="AJ103">
         <v>1</v>
       </c>
@@ -3877,8 +4015,14 @@
       <c r="A106">
         <v>1</v>
       </c>
+      <c r="E106">
+        <v>3</v>
+      </c>
       <c r="AJ106">
         <v>1</v>
+      </c>
+      <c r="AL106">
+        <v>3</v>
       </c>
       <c r="AS106">
         <v>1</v>
@@ -3924,6 +4068,12 @@
       <c r="AS107">
         <v>1</v>
       </c>
+      <c r="BM107">
+        <v>3</v>
+      </c>
+      <c r="BS107">
+        <v>3</v>
+      </c>
       <c r="CB107">
         <v>1</v>
       </c>
@@ -3961,6 +4111,12 @@
       <c r="A109">
         <v>1</v>
       </c>
+      <c r="E109">
+        <v>3</v>
+      </c>
+      <c r="I109">
+        <v>3</v>
+      </c>
       <c r="AJ109">
         <v>1</v>
       </c>
@@ -3990,6 +4146,9 @@
       <c r="AS110">
         <v>1</v>
       </c>
+      <c r="BU110">
+        <v>3</v>
+      </c>
       <c r="CB110">
         <v>1</v>
       </c>
@@ -4001,6 +4160,9 @@
       <c r="AJ111">
         <v>1</v>
       </c>
+      <c r="AQ111">
+        <v>3</v>
+      </c>
       <c r="AS111">
         <v>1</v>
       </c>
@@ -4030,6 +4192,12 @@
       <c r="A112">
         <v>1</v>
       </c>
+      <c r="J112">
+        <v>3</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
       <c r="AJ112">
         <v>1</v>
       </c>
@@ -4082,6 +4250,12 @@
       <c r="A114">
         <v>1</v>
       </c>
+      <c r="Y114">
+        <v>3</v>
+      </c>
+      <c r="AD114">
+        <v>3</v>
+      </c>
       <c r="AS114">
         <v>1</v>
       </c>
@@ -4334,6 +4508,12 @@
     <row r="119" spans="1:80" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>1</v>
+      </c>
+      <c r="AV119">
+        <v>3</v>
+      </c>
+      <c r="BB119">
+        <v>3</v>
       </c>
       <c r="CB119">
         <v>1</v>

--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF7B5AC-933B-4FB0-AA08-1721E96EE42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E742A74-299C-4CC8-8D73-DD308D100930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="75" yWindow="-14820" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>
@@ -1565,7 +1565,7 @@
       <c r="BE30">
         <v>1</v>
       </c>
-      <c r="BM30">
+      <c r="BN30">
         <v>3</v>
       </c>
       <c r="BT30">
@@ -1586,9 +1586,6 @@
         <v>3</v>
       </c>
       <c r="BE31">
-        <v>1</v>
-      </c>
-      <c r="BN31">
         <v>1</v>
       </c>
       <c r="BO31">

--- a/Rescource/Stage2.xlsx
+++ b/Rescource/Stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E742A74-299C-4CC8-8D73-DD308D100930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D004FC6E-1F4E-472B-971C-3CEDFDB209C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="75" yWindow="-14820" windowWidth="26850" windowHeight="14655" xr2:uid="{166AEAEC-8787-47DA-8182-3019AC7A1093}"/>
   </bookViews>
@@ -655,9 +655,6 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="AQ7">
-        <v>2</v>
-      </c>
       <c r="AR7">
         <v>2</v>
       </c>
@@ -710,9 +707,6 @@
         <v>2</v>
       </c>
       <c r="BS7">
-        <v>2</v>
-      </c>
-      <c r="BT7">
         <v>2</v>
       </c>
       <c r="CB7">
